--- a/survey_templates/036_return_to_in_person_learning_survey--survey_templates.xlsx
+++ b/survey_templates/036_return_to_in_person_learning_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>survey_header</t>
+          <t>introduction_to_in_person_learning</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Survey Header</t>
+          <t>Introduction to In Person Learning</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>what_is_your_level_of_in_person_learning</t>
+          <t>in_person_learning_experience</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What Is Your Level Of In Person Learning</t>
+          <t>In Person Learning Experience</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>how_long_do_you_agree_with_the_following</t>
+          <t>agreement_with_in_person_learning</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How Long Do You Agree With The Following</t>
+          <t>Agreement with In Person Learning</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>in_person_learning_enjoyed_your_learning_experience</t>
+          <t>in_person_learning_satisfaction</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>In Person Learning Enjoyed Your Learning Experience</t>
+          <t>In Person Learning Satisfaction</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>how_long_do_you_agree_with_the_following</t>
+          <t>frequency_of_in_person_learning</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How Long Do You Agree With The Following</t>
+          <t>Frequency of In Person Learning</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>how_long_do_you_agree_with_the_following_2</t>
+          <t>in_person_learning_benefits</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How Long Do You Agree With The Following</t>
+          <t>In Person Learning Benefits</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_2</t>
+          <t>open_ended_question</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>In Person Learning Enjoyed Your Learning Experience</t>
+          <t>Open-Ended Question</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_3</t>
+          <t>final_thoughts</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>In Person Learning Enjoyed Your Learning Experience</t>
+          <t>Final Thoughts</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,90 +699,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>how_long_do_you_agree_with_the_following_2</t>
+          <t>survey_instructions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How Long Do You Agree With The Following</t>
+          <t>Survey Instructions</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_4</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>In Person Learning Enjoyed Your Learning Experience</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>survey_footer</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Survey Footer</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_5</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>In Person Learning Enjoyed Your Learning Experience</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -799,10 +730,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -827,7 +758,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_choices</t>
+          <t>agreement_with_in_person_learning_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -844,7 +775,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_choices</t>
+          <t>agreement_with_in_person_learning_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -861,7 +792,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_choices</t>
+          <t>agreement_with_in_person_learning_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -878,7 +809,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_choices</t>
+          <t>agreement_with_in_person_learning_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -895,7 +826,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>how_long_do_you_agree_with_the_following_choices</t>
+          <t>in_person_learning_satisfaction_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -912,7 +843,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>how_long_do_you_agree_with_the_following_choices</t>
+          <t>in_person_learning_satisfaction_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -929,7 +860,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>how_long_do_you_agree_with_the_following_choices</t>
+          <t>in_person_learning_satisfaction_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -946,7 +877,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>how_long_do_you_agree_with_the_following_choices</t>
+          <t>in_person_learning_satisfaction_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -963,7 +894,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>how_long_do_you_agree_with_the_following_2_choices</t>
+          <t>frequency_of_in_person_learning_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -980,7 +911,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>how_long_do_you_agree_with_the_following_2_choices</t>
+          <t>frequency_of_in_person_learning_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -997,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>how_long_do_you_agree_with_the_following_2_choices</t>
+          <t>frequency_of_in_person_learning_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1014,7 +945,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>how_long_do_you_agree_with_the_following_2_choices</t>
+          <t>frequency_of_in_person_learning_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1023,346 +954,6 @@
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>No opinion</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_2_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>a_great_deal</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>A great deal</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_2_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>somewhat</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Somewhat</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_2_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>not_at_all</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Not at all</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_2_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no_opinion</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No opinion</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_3_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>a_great_deal</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>A great deal</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_3_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>somewhat</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Somewhat</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_3_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>not_at_all</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Not at all</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_3_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no_opinion</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No opinion</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>how_long_do_you_agree_with_the_following_2_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>a_great_deal</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>A great deal</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>how_long_do_you_agree_with_the_following_2_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>somewhat</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Somewhat</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>how_long_do_you_agree_with_the_following_2_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>not_at_all</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Not at all</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>how_long_do_you_agree_with_the_following_2_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no_opinion</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No opinion</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_4_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>a_great_deal</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>A great deal</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_4_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>somewhat</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Somewhat</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_4_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>not_at_all</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Not at all</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_4_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no_opinion</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No opinion</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_5_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>a_great_deal</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>A great deal</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_5_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>somewhat</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Somewhat</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_5_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>not_at_all</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Not at all</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>in_person_learning_enjoyed_your_learning_experience_5_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no_opinion</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
         <is>
           <t>No opinion</t>
         </is>
